--- a/data/raw/김포 25년/항공통계상세조회(노선) (3).xlsx
+++ b/data/raw/김포 25년/항공통계상세조회(노선) (3).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="69">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>10118</t>
-  </si>
-  <si>
-    <t>1729863</t>
-  </si>
-  <si>
-    <t>16136</t>
+    <t>5054</t>
+  </si>
+  <si>
+    <t>867963</t>
+  </si>
+  <si>
+    <t>7529</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,175 +53,172 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>373</t>
-  </si>
-  <si>
-    <t>70468</t>
-  </si>
-  <si>
-    <t>800</t>
+    <t>186</t>
+  </si>
+  <si>
+    <t>35453</t>
+  </si>
+  <si>
+    <t>381</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>6003</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>744</t>
+  </si>
+  <si>
+    <t>108655</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>4992</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>86124</t>
+  </si>
+  <si>
+    <t>2450</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>8356</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>4540</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>10279</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>8696</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>9747</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3127</t>
+  </si>
+  <si>
+    <t>553450</t>
+  </si>
+  <si>
+    <t>3569</t>
+  </si>
+  <si>
+    <t>청주(CJJ)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>6382</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>1155</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
+  </si>
+  <si>
     <t>124</t>
   </si>
   <si>
-    <t>12238</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1471</t>
-  </si>
-  <si>
-    <t>215250</t>
-  </si>
-  <si>
-    <t>734</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>10402</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>744</t>
-  </si>
-  <si>
-    <t>171997</t>
-  </si>
-  <si>
-    <t>3459</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>19028</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>9698</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>20726</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>147</t>
-  </si>
-  <si>
-    <t>17176</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>19697</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>6276</t>
-  </si>
-  <si>
-    <t>1098033</t>
-  </si>
-  <si>
-    <t>9334</t>
-  </si>
-  <si>
-    <t>청주(CJJ)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>13078</t>
-  </si>
-  <si>
-    <t>158</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>2410</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>49662</t>
-  </si>
-  <si>
-    <t>880</t>
+    <t>24131</t>
+  </si>
+  <si>
+    <t>282</t>
   </si>
 </sst>
 </file>
@@ -486,13 +483,13 @@
         <v>43</v>
       </c>
       <c r="D11" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="E11" t="s" s="0">
+      <c r="F11" t="s" s="0">
         <v>45</v>
-      </c>
-      <c r="F11" t="s" s="0">
-        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -503,16 +500,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="D12" t="s" s="0">
+      <c r="E12" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="E12" t="s" s="0">
+      <c r="F12" t="s" s="0">
         <v>49</v>
-      </c>
-      <c r="F12" t="s" s="0">
-        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -523,16 +520,16 @@
         <v>11</v>
       </c>
       <c r="C13" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="D13" t="s" s="0">
+      <c r="E13" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="E13" t="s" s="0">
+      <c r="F13" t="s" s="0">
         <v>53</v>
-      </c>
-      <c r="F13" t="s" s="0">
-        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -543,16 +540,16 @@
         <v>11</v>
       </c>
       <c r="C14" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="D14" t="s" s="0">
+      <c r="E14" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="E14" t="s" s="0">
-        <v>57</v>
-      </c>
       <c r="F14" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -563,16 +560,16 @@
         <v>11</v>
       </c>
       <c r="C15" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="D15" t="s" s="0">
+      <c r="E15" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="E15" t="s" s="0">
+      <c r="F15" t="s" s="0">
         <v>60</v>
-      </c>
-      <c r="F15" t="s" s="0">
-        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -583,16 +580,16 @@
         <v>11</v>
       </c>
       <c r="C16" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="D16" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="D16" t="s" s="0">
+      <c r="E16" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="E16" t="s" s="0">
+      <c r="F16" t="s" s="0">
         <v>64</v>
-      </c>
-      <c r="F16" t="s" s="0">
-        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -603,16 +600,16 @@
         <v>11</v>
       </c>
       <c r="C17" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="D17" t="s" s="0">
+      <c r="E17" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="E17" t="s" s="0">
+      <c r="F17" t="s" s="0">
         <v>68</v>
-      </c>
-      <c r="F17" t="s" s="0">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
